--- a/data/results/colored_output.xlsx
+++ b/data/results/colored_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isaktruedson/direct_repo/data/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E02D6E9-5354-E54A-86A4-930350E980BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324A5B46-B097-D54A-B9C2-7E17C165D298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="15220" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="15220" windowHeight="11980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparison" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4037" uniqueCount="934">
   <si>
     <t>Model</t>
   </si>
@@ -2829,6 +2829,12 @@
   </si>
   <si>
     <t>Baseline comparator can be pre intervention or Treatment as usual</t>
+  </si>
+  <si>
+    <t>Outcome unclear based on numerical values</t>
+  </si>
+  <si>
+    <t>Inference from CI</t>
   </si>
 </sst>
 </file>
@@ -11988,6 +11994,12 @@
       <c r="V183">
         <v>246</v>
       </c>
+      <c r="W183" t="s">
+        <v>926</v>
+      </c>
+      <c r="X183" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="184" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
@@ -12039,6 +12051,9 @@
       </c>
       <c r="V184">
         <v>246</v>
+      </c>
+      <c r="X184" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="185" spans="1:24" x14ac:dyDescent="0.2">
